--- a/results/-1Fold_links.xlsx
+++ b/results/-1Fold_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,6 +599,78 @@
         <v>0.03294370432794035</v>
       </c>
       <c r="T2" t="n">
+        <v>2.012818098068237</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>links</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>clisurv-po</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>256</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>gelu</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8892478863356501</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8680507227411308</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9424738289196055</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1118541458758656</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.03294370432794035</v>
+      </c>
+      <c r="T3" t="n">
         <v>2.012818098068237</v>
       </c>
     </row>
